--- a/Actieplan_Python.xlsx
+++ b/Actieplan_Python.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f020cdb928d38096/Programmeren/Odisee/LevensLang_Leren/LLL-BartBrondeel-2526/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{482E40B1-4C12-41F6-8D36-DD9DCD6004AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EDE279F-45DC-49D4-B35C-B780924A38B7}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{482E40B1-4C12-41F6-8D36-DD9DCD6004AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F4B940C-D4A4-4104-A515-B53985C6F9EE}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -755,7 +755,7 @@
       <c r="H4" s="10"/>
       <c r="I4" s="10">
         <f>('Werkelijke uren'!D32)</f>
-        <v>30.5</v>
+        <v>32.25</v>
       </c>
       <c r="J4" s="10" t="s">
         <v>21</v>
@@ -830,7 +830,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10">
         <f>('Werkelijke uren'!C103)</f>
-        <v>30.5</v>
+        <v>32.25</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="I22">
         <f>SUM(I7,I14,I20)</f>
-        <v>30.5</v>
+        <v>32.25</v>
       </c>
     </row>
   </sheetData>
@@ -1283,6 +1283,9 @@
       <c r="B17">
         <v>15</v>
       </c>
+      <c r="C17">
+        <v>1.75</v>
+      </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18">
@@ -1360,7 +1363,7 @@
       </c>
       <c r="D32">
         <f>SUM(C3:C32)</f>
-        <v>30.5</v>
+        <v>32.25</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.25">
@@ -1727,7 +1730,7 @@
       </c>
       <c r="C103">
         <f>SUM(C3:C102)</f>
-        <v>30.5</v>
+        <v>32.25</v>
       </c>
     </row>
   </sheetData>

--- a/Actieplan_Python.xlsx
+++ b/Actieplan_Python.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f020cdb928d38096/Programmeren/Odisee/LevensLang_Leren/LLL-BartBrondeel-2526/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{482E40B1-4C12-41F6-8D36-DD9DCD6004AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F4B940C-D4A4-4104-A515-B53985C6F9EE}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:1_{482E40B1-4C12-41F6-8D36-DD9DCD6004AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2ECD67D8-523A-45D9-ABE9-5625A76A6D1E}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Actieplan" sheetId="1" r:id="rId1"/>
@@ -755,7 +755,7 @@
       <c r="H4" s="10"/>
       <c r="I4" s="10">
         <f>('Werkelijke uren'!D32)</f>
-        <v>32.25</v>
+        <v>56.25</v>
       </c>
       <c r="J4" s="10" t="s">
         <v>21</v>
@@ -830,7 +830,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10">
         <f>('Werkelijke uren'!C103)</f>
-        <v>32.25</v>
+        <v>56.25</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="I22">
         <f>SUM(I7,I14,I20)</f>
-        <v>32.25</v>
+        <v>56.25</v>
       </c>
     </row>
   </sheetData>
@@ -1172,7 +1172,7 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
@@ -1180,7 +1180,7 @@
         <v>2</v>
       </c>
       <c r="C4">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
@@ -1188,7 +1188,7 @@
         <v>3</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
@@ -1196,7 +1196,7 @@
         <v>4</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
@@ -1204,7 +1204,7 @@
         <v>5</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
@@ -1212,7 +1212,7 @@
         <v>6</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
@@ -1220,7 +1220,7 @@
         <v>7</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
@@ -1228,7 +1228,7 @@
         <v>8</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
@@ -1236,7 +1236,7 @@
         <v>9</v>
       </c>
       <c r="C11">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
@@ -1244,7 +1244,7 @@
         <v>10</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
@@ -1252,7 +1252,7 @@
         <v>11</v>
       </c>
       <c r="C13">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
@@ -1260,7 +1260,7 @@
         <v>12</v>
       </c>
       <c r="C14">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
@@ -1268,7 +1268,7 @@
         <v>13</v>
       </c>
       <c r="C15">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
@@ -1276,7 +1276,7 @@
         <v>14</v>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
@@ -1284,23 +1284,32 @@
         <v>15</v>
       </c>
       <c r="C17">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18">
         <v>16</v>
       </c>
+      <c r="C18">
+        <v>3</v>
+      </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19">
         <v>17</v>
       </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20">
         <v>18</v>
       </c>
+      <c r="C20">
+        <v>4</v>
+      </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21">
@@ -1363,7 +1372,7 @@
       </c>
       <c r="D32">
         <f>SUM(C3:C32)</f>
-        <v>32.25</v>
+        <v>56.25</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.25">
@@ -1730,7 +1739,7 @@
       </c>
       <c r="C103">
         <f>SUM(C3:C102)</f>
-        <v>32.25</v>
+        <v>56.25</v>
       </c>
     </row>
   </sheetData>

--- a/Actieplan_Python.xlsx
+++ b/Actieplan_Python.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f020cdb928d38096/Programmeren/Odisee/LevensLang_Leren/LLL-BartBrondeel-2526/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:1_{482E40B1-4C12-41F6-8D36-DD9DCD6004AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2ECD67D8-523A-45D9-ABE9-5625A76A6D1E}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{482E40B1-4C12-41F6-8D36-DD9DCD6004AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9C55236-F87E-4B83-9568-C9E4BC90B38B}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -755,7 +755,7 @@
       <c r="H4" s="10"/>
       <c r="I4" s="10">
         <f>('Werkelijke uren'!D32)</f>
-        <v>56.25</v>
+        <v>58.25</v>
       </c>
       <c r="J4" s="10" t="s">
         <v>21</v>
@@ -830,7 +830,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10">
         <f>('Werkelijke uren'!C103)</f>
-        <v>56.25</v>
+        <v>58.25</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="I22">
         <f>SUM(I7,I14,I20)</f>
-        <v>56.25</v>
+        <v>58.25</v>
       </c>
     </row>
   </sheetData>
@@ -1315,6 +1315,9 @@
       <c r="B21">
         <v>19</v>
       </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22">
@@ -1372,7 +1375,7 @@
       </c>
       <c r="D32">
         <f>SUM(C3:C32)</f>
-        <v>56.25</v>
+        <v>58.25</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.25">
@@ -1739,7 +1742,7 @@
       </c>
       <c r="C103">
         <f>SUM(C3:C102)</f>
-        <v>56.25</v>
+        <v>58.25</v>
       </c>
     </row>
   </sheetData>

--- a/Actieplan_Python.xlsx
+++ b/Actieplan_Python.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f020cdb928d38096/Programmeren/Odisee/LevensLang_Leren/LLL-BartBrondeel-2526/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{482E40B1-4C12-41F6-8D36-DD9DCD6004AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9C55236-F87E-4B83-9568-C9E4BC90B38B}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{482E40B1-4C12-41F6-8D36-DD9DCD6004AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1EAD20B-2581-4E0C-BBD0-50C3CF73D34C}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -755,7 +755,7 @@
       <c r="H4" s="10"/>
       <c r="I4" s="10">
         <f>('Werkelijke uren'!D32)</f>
-        <v>58.25</v>
+        <v>63.25</v>
       </c>
       <c r="J4" s="10" t="s">
         <v>21</v>
@@ -830,7 +830,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10">
         <f>('Werkelijke uren'!C103)</f>
-        <v>58.25</v>
+        <v>63.25</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="I22">
         <f>SUM(I7,I14,I20)</f>
-        <v>58.25</v>
+        <v>63.25</v>
       </c>
     </row>
   </sheetData>
@@ -1323,11 +1323,17 @@
       <c r="B22">
         <v>20</v>
       </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23">
         <v>21</v>
       </c>
+      <c r="C23">
+        <v>3</v>
+      </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B24">
@@ -1375,7 +1381,7 @@
       </c>
       <c r="D32">
         <f>SUM(C3:C32)</f>
-        <v>58.25</v>
+        <v>63.25</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.25">
@@ -1742,7 +1748,7 @@
       </c>
       <c r="C103">
         <f>SUM(C3:C102)</f>
-        <v>58.25</v>
+        <v>63.25</v>
       </c>
     </row>
   </sheetData>

--- a/Actieplan_Python.xlsx
+++ b/Actieplan_Python.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f020cdb928d38096/Programmeren/Odisee/LevensLang_Leren/LLL-BartBrondeel-2526/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{482E40B1-4C12-41F6-8D36-DD9DCD6004AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1EAD20B-2581-4E0C-BBD0-50C3CF73D34C}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{482E40B1-4C12-41F6-8D36-DD9DCD6004AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A56C1EA-5440-4641-8FBA-9DD727488335}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Actieplan" sheetId="1" r:id="rId1"/>
@@ -755,7 +755,7 @@
       <c r="H4" s="10"/>
       <c r="I4" s="10">
         <f>('Werkelijke uren'!D32)</f>
-        <v>63.25</v>
+        <v>65.25</v>
       </c>
       <c r="J4" s="10" t="s">
         <v>21</v>
@@ -830,7 +830,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10">
         <f>('Werkelijke uren'!C103)</f>
-        <v>63.25</v>
+        <v>65.25</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="I22">
         <f>SUM(I7,I14,I20)</f>
-        <v>63.25</v>
+        <v>65.25</v>
       </c>
     </row>
   </sheetData>
@@ -1339,6 +1339,9 @@
       <c r="B24">
         <v>22</v>
       </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B25">
@@ -1381,7 +1384,7 @@
       </c>
       <c r="D32">
         <f>SUM(C3:C32)</f>
-        <v>63.25</v>
+        <v>65.25</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.25">
@@ -1748,7 +1751,7 @@
       </c>
       <c r="C103">
         <f>SUM(C3:C102)</f>
-        <v>63.25</v>
+        <v>65.25</v>
       </c>
     </row>
   </sheetData>

--- a/Actieplan_Python.xlsx
+++ b/Actieplan_Python.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f020cdb928d38096/Programmeren/Odisee/LevensLang_Leren/LLL-BartBrondeel-2526/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{482E40B1-4C12-41F6-8D36-DD9DCD6004AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A56C1EA-5440-4641-8FBA-9DD727488335}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{482E40B1-4C12-41F6-8D36-DD9DCD6004AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB829A31-A1B9-4135-868A-93BCF80844FB}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -755,7 +755,7 @@
       <c r="H4" s="10"/>
       <c r="I4" s="10">
         <f>('Werkelijke uren'!D32)</f>
-        <v>65.25</v>
+        <v>67.25</v>
       </c>
       <c r="J4" s="10" t="s">
         <v>21</v>
@@ -830,7 +830,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10">
         <f>('Werkelijke uren'!C103)</f>
-        <v>65.25</v>
+        <v>67.25</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="I22">
         <f>SUM(I7,I14,I20)</f>
-        <v>65.25</v>
+        <v>67.25</v>
       </c>
     </row>
   </sheetData>
@@ -1347,6 +1347,9 @@
       <c r="B25">
         <v>23</v>
       </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B26">
@@ -1384,7 +1387,7 @@
       </c>
       <c r="D32">
         <f>SUM(C3:C32)</f>
-        <v>65.25</v>
+        <v>67.25</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.25">
@@ -1751,7 +1754,7 @@
       </c>
       <c r="C103">
         <f>SUM(C3:C102)</f>
-        <v>65.25</v>
+        <v>67.25</v>
       </c>
     </row>
   </sheetData>

--- a/Actieplan_Python.xlsx
+++ b/Actieplan_Python.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f020cdb928d38096/Programmeren/Odisee/LevensLang_Leren/LLL-BartBrondeel-2526/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{482E40B1-4C12-41F6-8D36-DD9DCD6004AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB829A31-A1B9-4135-868A-93BCF80844FB}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{482E40B1-4C12-41F6-8D36-DD9DCD6004AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9531A664-465D-4C48-A169-E462E104971D}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -755,7 +755,7 @@
       <c r="H4" s="10"/>
       <c r="I4" s="10">
         <f>('Werkelijke uren'!D32)</f>
-        <v>67.25</v>
+        <v>69.25</v>
       </c>
       <c r="J4" s="10" t="s">
         <v>21</v>
@@ -830,7 +830,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10">
         <f>('Werkelijke uren'!C103)</f>
-        <v>67.25</v>
+        <v>69.25</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="I22">
         <f>SUM(I7,I14,I20)</f>
-        <v>67.25</v>
+        <v>69.25</v>
       </c>
     </row>
   </sheetData>
@@ -1355,6 +1355,9 @@
       <c r="B26">
         <v>24</v>
       </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B27">
@@ -1387,7 +1390,7 @@
       </c>
       <c r="D32">
         <f>SUM(C3:C32)</f>
-        <v>67.25</v>
+        <v>69.25</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.25">
@@ -1754,7 +1757,7 @@
       </c>
       <c r="C103">
         <f>SUM(C3:C102)</f>
-        <v>67.25</v>
+        <v>69.25</v>
       </c>
     </row>
   </sheetData>

--- a/Actieplan_Python.xlsx
+++ b/Actieplan_Python.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f020cdb928d38096/Programmeren/Odisee/LevensLang_Leren/LLL-BartBrondeel-2526/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{482E40B1-4C12-41F6-8D36-DD9DCD6004AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9531A664-465D-4C48-A169-E462E104971D}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{482E40B1-4C12-41F6-8D36-DD9DCD6004AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45CE3E06-DB97-46A6-B375-2D110C7FE290}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Actieplan" sheetId="1" r:id="rId1"/>
@@ -755,7 +755,7 @@
       <c r="H4" s="10"/>
       <c r="I4" s="10">
         <f>('Werkelijke uren'!D32)</f>
-        <v>69.25</v>
+        <v>72.25</v>
       </c>
       <c r="J4" s="10" t="s">
         <v>21</v>
@@ -830,7 +830,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10">
         <f>('Werkelijke uren'!C103)</f>
-        <v>69.25</v>
+        <v>72.25</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="I22">
         <f>SUM(I7,I14,I20)</f>
-        <v>69.25</v>
+        <v>72.25</v>
       </c>
     </row>
   </sheetData>
@@ -1363,6 +1363,9 @@
       <c r="B27">
         <v>25</v>
       </c>
+      <c r="C27">
+        <v>3</v>
+      </c>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B28">
@@ -1390,7 +1393,7 @@
       </c>
       <c r="D32">
         <f>SUM(C3:C32)</f>
-        <v>69.25</v>
+        <v>72.25</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.25">
@@ -1757,7 +1760,7 @@
       </c>
       <c r="C103">
         <f>SUM(C3:C102)</f>
-        <v>69.25</v>
+        <v>72.25</v>
       </c>
     </row>
   </sheetData>

--- a/Actieplan_Python.xlsx
+++ b/Actieplan_Python.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f020cdb928d38096/Programmeren/Odisee/LevensLang_Leren/LLL-BartBrondeel-2526/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{482E40B1-4C12-41F6-8D36-DD9DCD6004AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45CE3E06-DB97-46A6-B375-2D110C7FE290}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="13_ncr:1_{482E40B1-4C12-41F6-8D36-DD9DCD6004AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F9C7BA7-F877-40A1-8352-86D7F60BF184}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Actieplan" sheetId="1" r:id="rId1"/>
@@ -755,7 +755,7 @@
       <c r="H4" s="10"/>
       <c r="I4" s="10">
         <f>('Werkelijke uren'!D32)</f>
-        <v>72.25</v>
+        <v>75.25</v>
       </c>
       <c r="J4" s="10" t="s">
         <v>21</v>
@@ -830,7 +830,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10">
         <f>('Werkelijke uren'!C103)</f>
-        <v>72.25</v>
+        <v>75.25</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="I22">
         <f>SUM(I7,I14,I20)</f>
-        <v>72.25</v>
+        <v>75.25</v>
       </c>
     </row>
   </sheetData>
@@ -1371,6 +1371,9 @@
       <c r="B28">
         <v>26</v>
       </c>
+      <c r="C28">
+        <v>3</v>
+      </c>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B29">
@@ -1393,7 +1396,7 @@
       </c>
       <c r="D32">
         <f>SUM(C3:C32)</f>
-        <v>72.25</v>
+        <v>75.25</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.25">
@@ -1760,7 +1763,7 @@
       </c>
       <c r="C103">
         <f>SUM(C3:C102)</f>
-        <v>72.25</v>
+        <v>75.25</v>
       </c>
     </row>
   </sheetData>

--- a/Actieplan_Python.xlsx
+++ b/Actieplan_Python.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f020cdb928d38096/Programmeren/Odisee/LevensLang_Leren/LLL-BartBrondeel-2526/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="13_ncr:1_{482E40B1-4C12-41F6-8D36-DD9DCD6004AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F9C7BA7-F877-40A1-8352-86D7F60BF184}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="13_ncr:1_{482E40B1-4C12-41F6-8D36-DD9DCD6004AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34C25D81-B0A0-4934-8389-33BDFFAACDBD}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -755,7 +755,7 @@
       <c r="H4" s="10"/>
       <c r="I4" s="10">
         <f>('Werkelijke uren'!D32)</f>
-        <v>75.25</v>
+        <v>77.25</v>
       </c>
       <c r="J4" s="10" t="s">
         <v>21</v>
@@ -830,7 +830,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10">
         <f>('Werkelijke uren'!C103)</f>
-        <v>75.25</v>
+        <v>77.25</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="I22">
         <f>SUM(I7,I14,I20)</f>
-        <v>75.25</v>
+        <v>77.25</v>
       </c>
     </row>
   </sheetData>
@@ -1379,6 +1379,9 @@
       <c r="B29">
         <v>27</v>
       </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30">
@@ -1396,7 +1399,7 @@
       </c>
       <c r="D32">
         <f>SUM(C3:C32)</f>
-        <v>75.25</v>
+        <v>77.25</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.25">
@@ -1763,7 +1766,7 @@
       </c>
       <c r="C103">
         <f>SUM(C3:C102)</f>
-        <v>75.25</v>
+        <v>77.25</v>
       </c>
     </row>
   </sheetData>

--- a/Actieplan_Python.xlsx
+++ b/Actieplan_Python.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f020cdb928d38096/Programmeren/Odisee/LevensLang_Leren/LLL-BartBrondeel-2526/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="13_ncr:1_{482E40B1-4C12-41F6-8D36-DD9DCD6004AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34C25D81-B0A0-4934-8389-33BDFFAACDBD}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="13_ncr:1_{482E40B1-4C12-41F6-8D36-DD9DCD6004AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5355F162-99A8-4F3C-B056-5FAE47857C50}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -755,7 +755,7 @@
       <c r="H4" s="10"/>
       <c r="I4" s="10">
         <f>('Werkelijke uren'!D32)</f>
-        <v>77.25</v>
+        <v>83.25</v>
       </c>
       <c r="J4" s="10" t="s">
         <v>21</v>
@@ -830,7 +830,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10">
         <f>('Werkelijke uren'!C103)</f>
-        <v>77.25</v>
+        <v>83.25</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="I22">
         <f>SUM(I7,I14,I20)</f>
-        <v>77.25</v>
+        <v>83.25</v>
       </c>
     </row>
   </sheetData>
@@ -1387,11 +1387,17 @@
       <c r="B30">
         <v>28</v>
       </c>
+      <c r="C30">
+        <v>3</v>
+      </c>
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B31">
         <v>29</v>
       </c>
+      <c r="C31">
+        <v>3</v>
+      </c>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B32">
@@ -1399,7 +1405,7 @@
       </c>
       <c r="D32">
         <f>SUM(C3:C32)</f>
-        <v>77.25</v>
+        <v>83.25</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.25">
@@ -1766,7 +1772,7 @@
       </c>
       <c r="C103">
         <f>SUM(C3:C102)</f>
-        <v>77.25</v>
+        <v>83.25</v>
       </c>
     </row>
   </sheetData>

--- a/Actieplan_Python.xlsx
+++ b/Actieplan_Python.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f020cdb928d38096/Programmeren/Odisee/LevensLang_Leren/LLL-BartBrondeel-2526/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="13_ncr:1_{482E40B1-4C12-41F6-8D36-DD9DCD6004AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5355F162-99A8-4F3C-B056-5FAE47857C50}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="13_ncr:1_{482E40B1-4C12-41F6-8D36-DD9DCD6004AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37309C5F-A0DF-41FD-A4BF-2ACDCDB2A83A}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Actieplan" sheetId="1" r:id="rId1"/>
@@ -755,7 +755,7 @@
       <c r="H4" s="10"/>
       <c r="I4" s="10">
         <f>('Werkelijke uren'!D32)</f>
-        <v>83.25</v>
+        <v>85.25</v>
       </c>
       <c r="J4" s="10" t="s">
         <v>21</v>
@@ -830,7 +830,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10">
         <f>('Werkelijke uren'!C103)</f>
-        <v>83.25</v>
+        <v>85.25</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="I22">
         <f>SUM(I7,I14,I20)</f>
-        <v>83.25</v>
+        <v>85.25</v>
       </c>
     </row>
   </sheetData>
@@ -1403,9 +1403,12 @@
       <c r="B32">
         <v>30</v>
       </c>
+      <c r="C32">
+        <v>2</v>
+      </c>
       <c r="D32">
         <f>SUM(C3:C32)</f>
-        <v>83.25</v>
+        <v>85.25</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.25">
@@ -1772,7 +1775,7 @@
       </c>
       <c r="C103">
         <f>SUM(C3:C102)</f>
-        <v>83.25</v>
+        <v>85.25</v>
       </c>
     </row>
   </sheetData>

--- a/Actieplan_Python.xlsx
+++ b/Actieplan_Python.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f020cdb928d38096/Programmeren/Odisee/LevensLang_Leren/LLL-BartBrondeel-2526/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="13_ncr:1_{482E40B1-4C12-41F6-8D36-DD9DCD6004AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37309C5F-A0DF-41FD-A4BF-2ACDCDB2A83A}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="13_ncr:1_{482E40B1-4C12-41F6-8D36-DD9DCD6004AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{900596C3-3D69-4CC9-8CCE-659E9BA1262C}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Actieplan" sheetId="1" r:id="rId1"/>
@@ -784,7 +784,7 @@
       <c r="H5" s="10"/>
       <c r="I5" s="10">
         <f>('Werkelijke uren'!D62)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J5" s="10" t="s">
         <v>22</v>
@@ -830,7 +830,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10">
         <f>('Werkelijke uren'!C103)</f>
-        <v>85.25</v>
+        <v>90.25</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="I22">
         <f>SUM(I7,I14,I20)</f>
-        <v>85.25</v>
+        <v>90.25</v>
       </c>
     </row>
   </sheetData>
@@ -1411,82 +1411,88 @@
         <v>85.25</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34">
         <v>32</v>
       </c>
-    </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35">
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36">
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37">
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38">
         <v>36</v>
       </c>
     </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39">
         <v>37</v>
       </c>
     </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40">
         <v>38</v>
       </c>
     </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B41">
         <v>39</v>
       </c>
     </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B42">
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B43">
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B44">
         <v>42</v>
       </c>
     </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B45">
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B46">
         <v>44</v>
       </c>
     </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B47">
         <v>45</v>
       </c>
     </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B48">
         <v>46</v>
       </c>
@@ -1562,7 +1568,7 @@
       </c>
       <c r="D62">
         <f>SUM(C33:C62)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
@@ -1775,7 +1781,7 @@
       </c>
       <c r="C103">
         <f>SUM(C3:C102)</f>
-        <v>85.25</v>
+        <v>90.25</v>
       </c>
     </row>
   </sheetData>

--- a/Actieplan_Python.xlsx
+++ b/Actieplan_Python.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f020cdb928d38096/Programmeren/Odisee/LevensLang_Leren/LLL-BartBrondeel-2526/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="13_ncr:1_{482E40B1-4C12-41F6-8D36-DD9DCD6004AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{900596C3-3D69-4CC9-8CCE-659E9BA1262C}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="13_ncr:1_{482E40B1-4C12-41F6-8D36-DD9DCD6004AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16586C5A-377B-42EF-86B9-3379F31DD4B2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -784,7 +784,7 @@
       <c r="H5" s="10"/>
       <c r="I5" s="10">
         <f>('Werkelijke uren'!D62)</f>
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J5" s="10" t="s">
         <v>22</v>
@@ -830,7 +830,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10">
         <f>('Werkelijke uren'!C103)</f>
-        <v>90.25</v>
+        <v>96.25</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="I22">
         <f>SUM(I7,I14,I20)</f>
-        <v>90.25</v>
+        <v>96.25</v>
       </c>
     </row>
   </sheetData>
@@ -1431,11 +1431,17 @@
       <c r="B35">
         <v>33</v>
       </c>
+      <c r="C35">
+        <v>3</v>
+      </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36">
         <v>34</v>
       </c>
+      <c r="C36">
+        <v>3</v>
+      </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37">
@@ -1568,7 +1574,7 @@
       </c>
       <c r="D62">
         <f>SUM(C33:C62)</f>
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
@@ -1781,7 +1787,7 @@
       </c>
       <c r="C103">
         <f>SUM(C3:C102)</f>
-        <v>90.25</v>
+        <v>96.25</v>
       </c>
     </row>
   </sheetData>
